--- a/Team-Data/2008-09/1-5-2008-09.xlsx
+++ b/Team-Data/2008-09/1-5-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -742,13 +809,13 @@
         <v>16</v>
       </c>
       <c r="AE2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AF2" t="n">
         <v>6</v>
       </c>
       <c r="AG2" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH2" t="n">
         <v>23</v>
@@ -781,25 +848,25 @@
         <v>25</v>
       </c>
       <c r="AR2" t="n">
+        <v>18</v>
+      </c>
+      <c r="AS2" t="n">
         <v>17</v>
-      </c>
-      <c r="AS2" t="n">
-        <v>16</v>
       </c>
       <c r="AT2" t="n">
         <v>18</v>
       </c>
       <c r="AU2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AV2" t="n">
         <v>9</v>
       </c>
       <c r="AW2" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AX2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY2" t="n">
         <v>6</v>
@@ -808,13 +875,13 @@
         <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB2" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BC2" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="BD2" t="n">
         <v>10</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -843,97 +910,97 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="E3" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="F3" t="n">
         <v>6</v>
       </c>
       <c r="G3" t="n">
-        <v>0.824</v>
+        <v>0.829</v>
       </c>
       <c r="H3" t="n">
         <v>48.3</v>
       </c>
       <c r="I3" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J3" t="n">
         <v>75.90000000000001</v>
       </c>
       <c r="K3" t="n">
-        <v>0.484</v>
+        <v>0.483</v>
       </c>
       <c r="L3" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="M3" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N3" t="n">
-        <v>0.371</v>
+        <v>0.368</v>
       </c>
       <c r="O3" t="n">
         <v>21.6</v>
       </c>
       <c r="P3" t="n">
-        <v>28</v>
+        <v>28.1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.772</v>
+        <v>0.766</v>
       </c>
       <c r="R3" t="n">
         <v>10.7</v>
       </c>
       <c r="S3" t="n">
-        <v>32.6</v>
+        <v>32.4</v>
       </c>
       <c r="T3" t="n">
-        <v>43.3</v>
+        <v>43.1</v>
       </c>
       <c r="U3" t="n">
-        <v>22.2</v>
+        <v>22</v>
       </c>
       <c r="V3" t="n">
         <v>16.3</v>
       </c>
       <c r="W3" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="X3" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.6</v>
+        <v>4.5</v>
       </c>
       <c r="Z3" t="n">
-        <v>23</v>
+        <v>23.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>24</v>
+        <v>24.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.2</v>
+        <v>100.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>10.2</v>
+        <v>10</v>
       </c>
       <c r="AD3" t="n">
-        <v>9</v>
+        <v>1</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
       </c>
       <c r="AF3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AG3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AH3" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AI3" t="n">
         <v>12</v>
@@ -948,25 +1015,25 @@
         <v>19</v>
       </c>
       <c r="AM3" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN3" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP3" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AQ3" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AR3" t="n">
         <v>19</v>
       </c>
       <c r="AS3" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AT3" t="n">
         <v>6</v>
@@ -981,10 +1048,10 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="AY3" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AZ3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -1103,19 +1170,19 @@
         <v>-2.6</v>
       </c>
       <c r="AD4" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE4" t="n">
         <v>22</v>
       </c>
       <c r="AF4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AG4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH4" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1130,13 +1197,13 @@
         <v>21</v>
       </c>
       <c r="AM4" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AN4" t="n">
         <v>18</v>
       </c>
       <c r="AO4" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP4" t="n">
         <v>12</v>
@@ -1160,10 +1227,10 @@
         <v>23</v>
       </c>
       <c r="AW4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AY4" t="n">
         <v>29</v>
@@ -1178,7 +1245,7 @@
         <v>30</v>
       </c>
       <c r="BC4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD4" t="n">
         <v>10</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -1207,97 +1274,97 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E5" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="F5" t="n">
         <v>20</v>
       </c>
       <c r="G5" t="n">
-        <v>0.394</v>
+        <v>0.412</v>
       </c>
       <c r="H5" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I5" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J5" t="n">
-        <v>84.40000000000001</v>
+        <v>84</v>
       </c>
       <c r="K5" t="n">
-        <v>0.44</v>
+        <v>0.442</v>
       </c>
       <c r="L5" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M5" t="n">
-        <v>16.8</v>
+        <v>16.6</v>
       </c>
       <c r="N5" t="n">
-        <v>0.384</v>
+        <v>0.385</v>
       </c>
       <c r="O5" t="n">
-        <v>18.5</v>
+        <v>18.9</v>
       </c>
       <c r="P5" t="n">
-        <v>23.2</v>
+        <v>23.8</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.796</v>
+        <v>0.794</v>
       </c>
       <c r="R5" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
         <v>41.9</v>
       </c>
       <c r="U5" t="n">
-        <v>19.8</v>
+        <v>20.1</v>
       </c>
       <c r="V5" t="n">
-        <v>14.9</v>
+        <v>15.1</v>
       </c>
       <c r="W5" t="n">
         <v>7.4</v>
       </c>
       <c r="X5" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="AA5" t="n">
-        <v>20</v>
+        <v>20.3</v>
       </c>
       <c r="AB5" t="n">
-        <v>99.3</v>
+        <v>99.5</v>
       </c>
       <c r="AC5" t="n">
-        <v>-4.3</v>
+        <v>-3.8</v>
       </c>
       <c r="AD5" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AE5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AF5" t="n">
         <v>19</v>
       </c>
       <c r="AG5" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AH5" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI5" t="n">
         <v>9</v>
@@ -1312,37 +1379,37 @@
         <v>16</v>
       </c>
       <c r="AM5" t="n">
+        <v>20</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>4</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>15</v>
+      </c>
+      <c r="AP5" t="n">
         <v>19</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>5</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>17</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>22</v>
       </c>
       <c r="AQ5" t="n">
         <v>7</v>
       </c>
       <c r="AR5" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AT5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AU5" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AV5" t="n">
         <v>18</v>
       </c>
       <c r="AW5" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AX5" t="n">
         <v>7</v>
@@ -1354,10 +1421,10 @@
         <v>23</v>
       </c>
       <c r="BA5" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="BC5" t="n">
         <v>23</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -1389,103 +1456,103 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E6" t="n">
         <v>27</v>
       </c>
       <c r="F6" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="G6" t="n">
-        <v>0.844</v>
+        <v>0.8179999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48</v>
       </c>
       <c r="I6" t="n">
-        <v>37.6</v>
+        <v>37.4</v>
       </c>
       <c r="J6" t="n">
-        <v>78.90000000000001</v>
+        <v>78.59999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.477</v>
+        <v>0.475</v>
       </c>
       <c r="L6" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.346</v>
+        <v>0.343</v>
       </c>
       <c r="O6" t="n">
-        <v>19.3</v>
+        <v>19.4</v>
       </c>
       <c r="P6" t="n">
-        <v>25.1</v>
+        <v>25.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.766</v>
+        <v>0.765</v>
       </c>
       <c r="R6" t="n">
-        <v>11.2</v>
+        <v>11.1</v>
       </c>
       <c r="S6" t="n">
-        <v>30.8</v>
+        <v>30.9</v>
       </c>
       <c r="T6" t="n">
         <v>42</v>
       </c>
       <c r="U6" t="n">
-        <v>20.7</v>
+        <v>20.5</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
         <v>8</v>
       </c>
       <c r="X6" t="n">
-        <v>6.1</v>
+        <v>6</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.5</v>
+        <v>3.4</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.4</v>
+        <v>20.6</v>
       </c>
       <c r="AA6" t="n">
-        <v>21</v>
+        <v>21.2</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.7</v>
+        <v>101.2</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.3</v>
+        <v>11.8</v>
       </c>
       <c r="AD6" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
       </c>
       <c r="AF6" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AG6" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AH6" t="n">
         <v>27</v>
       </c>
       <c r="AI6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK6" t="n">
         <v>3</v>
@@ -1494,7 +1561,7 @@
         <v>9</v>
       </c>
       <c r="AM6" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AN6" t="n">
         <v>20</v>
@@ -1506,7 +1573,7 @@
         <v>11</v>
       </c>
       <c r="AQ6" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AR6" t="n">
         <v>15</v>
@@ -1515,28 +1582,28 @@
         <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AU6" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AV6" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AW6" t="n">
         <v>7</v>
       </c>
       <c r="AX6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AY6" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
         <v>7</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -1664,16 +1731,16 @@
         <v>8</v>
       </c>
       <c r="AI7" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AJ7" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AK7" t="n">
         <v>16</v>
       </c>
       <c r="AL7" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AM7" t="n">
         <v>7</v>
@@ -1682,7 +1749,7 @@
         <v>23</v>
       </c>
       <c r="AO7" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AP7" t="n">
         <v>29</v>
@@ -1712,16 +1779,16 @@
         <v>11</v>
       </c>
       <c r="AY7" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BA7" t="n">
         <v>27</v>
       </c>
       <c r="BB7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BC7" t="n">
         <v>12</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -1753,64 +1820,64 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F8" t="n">
         <v>12</v>
       </c>
       <c r="G8" t="n">
-        <v>0.667</v>
+        <v>0.657</v>
       </c>
       <c r="H8" t="n">
         <v>48.1</v>
       </c>
       <c r="I8" t="n">
-        <v>37.2</v>
+        <v>36.8</v>
       </c>
       <c r="J8" t="n">
-        <v>78.3</v>
+        <v>78.09999999999999</v>
       </c>
       <c r="K8" t="n">
-        <v>0.474</v>
+        <v>0.471</v>
       </c>
       <c r="L8" t="n">
         <v>6.9</v>
       </c>
       <c r="M8" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="N8" t="n">
-        <v>0.386</v>
+        <v>0.385</v>
       </c>
       <c r="O8" t="n">
         <v>22.9</v>
       </c>
       <c r="P8" t="n">
-        <v>30.2</v>
+        <v>30.1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.758</v>
+        <v>0.76</v>
       </c>
       <c r="R8" t="n">
-        <v>10.2</v>
+        <v>10.3</v>
       </c>
       <c r="S8" t="n">
-        <v>30.4</v>
+        <v>30.1</v>
       </c>
       <c r="T8" t="n">
-        <v>40.6</v>
+        <v>40.4</v>
       </c>
       <c r="U8" t="n">
-        <v>22.9</v>
+        <v>22.5</v>
       </c>
       <c r="V8" t="n">
         <v>15.5</v>
       </c>
       <c r="W8" t="n">
-        <v>8.800000000000001</v>
+        <v>8.9</v>
       </c>
       <c r="X8" t="n">
         <v>5.9</v>
@@ -1825,10 +1892,10 @@
         <v>23.3</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.2</v>
+        <v>103.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.7</v>
+        <v>3.2</v>
       </c>
       <c r="AD8" t="n">
         <v>1</v>
@@ -1840,28 +1907,28 @@
         <v>9</v>
       </c>
       <c r="AG8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="AH8" t="n">
         <v>26</v>
       </c>
       <c r="AI8" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AJ8" t="n">
         <v>25</v>
       </c>
       <c r="AK8" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AL8" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AM8" t="n">
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,16 +1937,16 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AR8" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AS8" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AT8" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AU8" t="n">
         <v>3</v>
@@ -1891,7 +1958,7 @@
         <v>3</v>
       </c>
       <c r="AX8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY8" t="n">
         <v>25</v>
@@ -1903,10 +1970,10 @@
         <v>4</v>
       </c>
       <c r="BB8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BC8" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -2028,16 +2095,16 @@
         <v>15</v>
       </c>
       <c r="AI9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AJ9" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AK9" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AL9" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AM9" t="n">
         <v>27</v>
@@ -2049,16 +2116,16 @@
         <v>25</v>
       </c>
       <c r="AP9" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ9" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AR9" t="n">
         <v>22</v>
       </c>
       <c r="AS9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AT9" t="n">
         <v>20</v>
@@ -2070,7 +2137,7 @@
         <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX9" t="n">
         <v>9</v>
@@ -2088,7 +2155,7 @@
         <v>24</v>
       </c>
       <c r="BC9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -2117,16 +2184,16 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E10" t="n">
         <v>10</v>
       </c>
       <c r="F10" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G10" t="n">
-        <v>0.278</v>
+        <v>0.286</v>
       </c>
       <c r="H10" t="n">
         <v>48.4</v>
@@ -2135,37 +2202,37 @@
         <v>38.3</v>
       </c>
       <c r="J10" t="n">
-        <v>86.09999999999999</v>
+        <v>86.3</v>
       </c>
       <c r="K10" t="n">
-        <v>0.445</v>
+        <v>0.444</v>
       </c>
       <c r="L10" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M10" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="N10" t="n">
-        <v>0.341</v>
+        <v>0.338</v>
       </c>
       <c r="O10" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="P10" t="n">
-        <v>29.6</v>
+        <v>29.5</v>
       </c>
       <c r="Q10" t="n">
         <v>0.762</v>
       </c>
       <c r="R10" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="S10" t="n">
         <v>29.6</v>
       </c>
       <c r="T10" t="n">
-        <v>42.3</v>
+        <v>42.4</v>
       </c>
       <c r="U10" t="n">
         <v>20</v>
@@ -2177,22 +2244,22 @@
         <v>8.4</v>
       </c>
       <c r="X10" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Y10" t="n">
         <v>5.9</v>
       </c>
       <c r="Z10" t="n">
-        <v>21.3</v>
+        <v>21.1</v>
       </c>
       <c r="AA10" t="n">
-        <v>24.4</v>
+        <v>24.5</v>
       </c>
       <c r="AB10" t="n">
-        <v>105.5</v>
+        <v>105.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-5.9</v>
+        <v>-6</v>
       </c>
       <c r="AD10" t="n">
         <v>1</v>
@@ -2201,7 +2268,7 @@
         <v>25</v>
       </c>
       <c r="AF10" t="n">
-        <v>28</v>
+        <v>25</v>
       </c>
       <c r="AG10" t="n">
         <v>25</v>
@@ -2213,10 +2280,10 @@
         <v>3</v>
       </c>
       <c r="AJ10" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AK10" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AL10" t="n">
         <v>18</v>
@@ -2234,22 +2301,22 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR10" t="n">
         <v>3</v>
       </c>
       <c r="AS10" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT10" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AU10" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AV10" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW10" t="n">
         <v>5</v>
@@ -2261,7 +2328,7 @@
         <v>28</v>
       </c>
       <c r="AZ10" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="BA10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -2377,16 +2444,16 @@
         <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE11" t="n">
         <v>8</v>
       </c>
       <c r="AF11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AG11" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AH11" t="n">
         <v>12</v>
@@ -2404,7 +2471,7 @@
         <v>8</v>
       </c>
       <c r="AM11" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AN11" t="n">
         <v>10</v>
@@ -2422,7 +2489,7 @@
         <v>23</v>
       </c>
       <c r="AS11" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AT11" t="n">
         <v>7</v>
@@ -2434,22 +2501,22 @@
         <v>13</v>
       </c>
       <c r="AW11" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
       </c>
       <c r="AY11" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA11" t="n">
         <v>13</v>
       </c>
       <c r="BB11" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BC11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -2481,61 +2548,61 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E12" t="n">
         <v>12</v>
       </c>
       <c r="F12" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="G12" t="n">
-        <v>0.353</v>
+        <v>0.364</v>
       </c>
       <c r="H12" t="n">
-        <v>48.7</v>
+        <v>48.8</v>
       </c>
       <c r="I12" t="n">
         <v>39</v>
       </c>
       <c r="J12" t="n">
-        <v>86.3</v>
+        <v>86.09999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L12" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="M12" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0.357</v>
+        <v>0.355</v>
       </c>
       <c r="O12" t="n">
-        <v>18.2</v>
+        <v>18.1</v>
       </c>
       <c r="P12" t="n">
-        <v>22.7</v>
+        <v>22.5</v>
       </c>
       <c r="Q12" t="n">
         <v>0.802</v>
       </c>
       <c r="R12" t="n">
-        <v>11.9</v>
+        <v>12.1</v>
       </c>
       <c r="S12" t="n">
-        <v>32.6</v>
+        <v>32.8</v>
       </c>
       <c r="T12" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="U12" t="n">
-        <v>22.5</v>
+        <v>22.2</v>
       </c>
       <c r="V12" t="n">
-        <v>15.7</v>
+        <v>15.9</v>
       </c>
       <c r="W12" t="n">
         <v>7.1</v>
@@ -2544,22 +2611,22 @@
         <v>5.4</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Z12" t="n">
         <v>23.4</v>
       </c>
       <c r="AA12" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB12" t="n">
-        <v>103.3</v>
+        <v>102.9</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.5</v>
+        <v>-2</v>
       </c>
       <c r="AD12" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE12" t="n">
         <v>22</v>
@@ -2577,25 +2644,25 @@
         <v>2</v>
       </c>
       <c r="AJ12" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AK12" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AL12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AM12" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AN12" t="n">
         <v>17</v>
       </c>
       <c r="AO12" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AP12" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AQ12" t="n">
         <v>5</v>
@@ -2607,7 +2674,7 @@
         <v>2</v>
       </c>
       <c r="AT12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="n">
         <v>4</v>
@@ -2628,13 +2695,13 @@
         <v>27</v>
       </c>
       <c r="BA12" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BB12" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BC12" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -2765,10 +2832,10 @@
         <v>30</v>
       </c>
       <c r="AL13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AM13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AN13" t="n">
         <v>28</v>
@@ -2777,7 +2844,7 @@
         <v>26</v>
       </c>
       <c r="AP13" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ13" t="n">
         <v>23</v>
@@ -2786,10 +2853,10 @@
         <v>5</v>
       </c>
       <c r="AS13" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AT13" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AU13" t="n">
         <v>27</v>
@@ -2798,7 +2865,7 @@
         <v>17</v>
       </c>
       <c r="AW13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2810,7 +2877,7 @@
         <v>19</v>
       </c>
       <c r="BA13" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="BB13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -2845,94 +2912,94 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="E14" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="F14" t="n">
         <v>5</v>
       </c>
       <c r="G14" t="n">
-        <v>0.839</v>
+        <v>0.844</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>39.6</v>
+        <v>39.5</v>
       </c>
       <c r="J14" t="n">
-        <v>83.59999999999999</v>
+        <v>83.40000000000001</v>
       </c>
       <c r="K14" t="n">
-        <v>0.474</v>
+        <v>0.473</v>
       </c>
       <c r="L14" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="M14" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="N14" t="n">
-        <v>0.369</v>
+        <v>0.374</v>
       </c>
       <c r="O14" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="P14" t="n">
-        <v>28.3</v>
+        <v>28</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.765</v>
+        <v>0.767</v>
       </c>
       <c r="R14" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S14" t="n">
-        <v>32.3</v>
+        <v>32.5</v>
       </c>
       <c r="T14" t="n">
-        <v>44.6</v>
+        <v>44.8</v>
       </c>
       <c r="U14" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="V14" t="n">
         <v>14</v>
       </c>
       <c r="W14" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X14" t="n">
         <v>5.5</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.6</v>
+        <v>107.2</v>
       </c>
       <c r="AC14" t="n">
-        <v>9.6</v>
+        <v>9.9</v>
       </c>
       <c r="AD14" t="n">
-        <v>28</v>
+        <v>24</v>
       </c>
       <c r="AE14" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AF14" t="n">
         <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>27</v>
@@ -2941,10 +3008,10 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AK14" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AL14" t="n">
         <v>15</v>
@@ -2953,25 +3020,25 @@
         <v>14</v>
       </c>
       <c r="AN14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
         <v>7</v>
       </c>
       <c r="AS14" t="n">
-        <v>6</v>
+        <v>3</v>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
@@ -2986,10 +3053,10 @@
         <v>8</v>
       </c>
       <c r="AY14" t="n">
+        <v>9</v>
+      </c>
+      <c r="AZ14" t="n">
         <v>10</v>
-      </c>
-      <c r="AZ14" t="n">
-        <v>11</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-4.9</v>
       </c>
       <c r="AD15" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE15" t="n">
         <v>24</v>
@@ -3126,7 +3193,7 @@
         <v>26</v>
       </c>
       <c r="AK15" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AL15" t="n">
         <v>27</v>
@@ -3135,10 +3202,10 @@
         <v>26</v>
       </c>
       <c r="AN15" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AO15" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AP15" t="n">
         <v>12</v>
@@ -3162,13 +3229,13 @@
         <v>16</v>
       </c>
       <c r="AW15" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AX15" t="n">
         <v>22</v>
       </c>
       <c r="AY15" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AZ15" t="n">
         <v>20</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -3209,16 +3276,16 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E16" t="n">
         <v>18</v>
       </c>
       <c r="F16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="G16" t="n">
-        <v>0.545</v>
+        <v>0.5629999999999999</v>
       </c>
       <c r="H16" t="n">
         <v>48.3</v>
@@ -3233,76 +3300,76 @@
         <v>0.445</v>
       </c>
       <c r="L16" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M16" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N16" t="n">
         <v>0.349</v>
       </c>
       <c r="O16" t="n">
-        <v>17</v>
+        <v>17.3</v>
       </c>
       <c r="P16" t="n">
-        <v>23.1</v>
+        <v>23.6</v>
       </c>
       <c r="Q16" t="n">
         <v>0.735</v>
       </c>
       <c r="R16" t="n">
-        <v>10.8</v>
+        <v>11</v>
       </c>
       <c r="S16" t="n">
-        <v>29.8</v>
+        <v>29.7</v>
       </c>
       <c r="T16" t="n">
         <v>40.7</v>
       </c>
       <c r="U16" t="n">
-        <v>19.7</v>
+        <v>19.6</v>
       </c>
       <c r="V16" t="n">
         <v>12.9</v>
       </c>
       <c r="W16" t="n">
-        <v>8.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>5.8</v>
+        <v>5.9</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.4</v>
+        <v>4.5</v>
       </c>
       <c r="Z16" t="n">
-        <v>20.8</v>
+        <v>21.1</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.9</v>
+        <v>20.2</v>
       </c>
       <c r="AB16" t="n">
-        <v>95.59999999999999</v>
+        <v>96</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.2</v>
+        <v>0.4</v>
       </c>
       <c r="AD16" t="n">
-        <v>16</v>
+        <v>24</v>
       </c>
       <c r="AE16" t="n">
         <v>15</v>
       </c>
       <c r="AF16" t="n">
+        <v>12</v>
+      </c>
+      <c r="AG16" t="n">
         <v>14</v>
       </c>
-      <c r="AG16" t="n">
+      <c r="AH16" t="n">
         <v>15</v>
       </c>
-      <c r="AH16" t="n">
-        <v>16</v>
-      </c>
       <c r="AI16" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AJ16" t="n">
         <v>15</v>
@@ -3311,7 +3378,7 @@
         <v>18</v>
       </c>
       <c r="AL16" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM16" t="n">
         <v>9</v>
@@ -3320,19 +3387,19 @@
         <v>19</v>
       </c>
       <c r="AO16" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AQ16" t="n">
         <v>29</v>
       </c>
       <c r="AR16" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AT16" t="n">
         <v>21</v>
@@ -3347,16 +3414,16 @@
         <v>6</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY16" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AZ16" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA16" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="BB16" t="n">
         <v>22</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -3394,13 +3461,13 @@
         <v>35</v>
       </c>
       <c r="E17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="G17" t="n">
-        <v>0.486</v>
+        <v>0.457</v>
       </c>
       <c r="H17" t="n">
         <v>48.4</v>
@@ -3409,82 +3476,82 @@
         <v>35.9</v>
       </c>
       <c r="J17" t="n">
-        <v>81.7</v>
+        <v>81.59999999999999</v>
       </c>
       <c r="K17" t="n">
         <v>0.44</v>
       </c>
       <c r="L17" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="M17" t="n">
-        <v>15.2</v>
+        <v>14.8</v>
       </c>
       <c r="N17" t="n">
-        <v>0.337</v>
+        <v>0.335</v>
       </c>
       <c r="O17" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="P17" t="n">
-        <v>25.6</v>
+        <v>25.5</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.778</v>
+        <v>0.776</v>
       </c>
       <c r="R17" t="n">
-        <v>12.5</v>
+        <v>12.6</v>
       </c>
       <c r="S17" t="n">
-        <v>30.8</v>
+        <v>30.6</v>
       </c>
       <c r="T17" t="n">
-        <v>43.3</v>
+        <v>43.2</v>
       </c>
       <c r="U17" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="V17" t="n">
-        <v>15</v>
+        <v>15.3</v>
       </c>
       <c r="W17" t="n">
-        <v>7.1</v>
+        <v>7</v>
       </c>
       <c r="X17" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Y17" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.9</v>
+        <v>24.3</v>
       </c>
       <c r="AA17" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="AB17" t="n">
-        <v>96.90000000000001</v>
+        <v>96.5</v>
       </c>
       <c r="AC17" t="n">
-        <v>1.1</v>
+        <v>0.4</v>
       </c>
       <c r="AD17" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE17" t="n">
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AG17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AH17" t="n">
         <v>12</v>
       </c>
       <c r="AI17" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AJ17" t="n">
         <v>10</v>
@@ -3493,10 +3560,10 @@
         <v>24</v>
       </c>
       <c r="AL17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AM17" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="AN17" t="n">
         <v>22</v>
@@ -3505,7 +3572,7 @@
         <v>9</v>
       </c>
       <c r="AP17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AQ17" t="n">
         <v>10</v>
@@ -3517,22 +3584,22 @@
         <v>11</v>
       </c>
       <c r="AT17" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU17" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AV17" t="n">
+        <v>20</v>
+      </c>
+      <c r="AW17" t="n">
         <v>19</v>
       </c>
-      <c r="AW17" t="n">
-        <v>18</v>
-      </c>
       <c r="AX17" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AY17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AZ17" t="n">
         <v>30</v>
@@ -3541,10 +3608,10 @@
         <v>6</v>
       </c>
       <c r="BB17" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BC17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -3666,7 +3733,7 @@
         <v>5</v>
       </c>
       <c r="AI18" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AJ18" t="n">
         <v>8</v>
@@ -3678,7 +3745,7 @@
         <v>26</v>
       </c>
       <c r="AM18" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AN18" t="n">
         <v>26</v>
@@ -3687,16 +3754,16 @@
         <v>10</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AQ18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AR18" t="n">
         <v>8</v>
       </c>
       <c r="AS18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT18" t="n">
         <v>15</v>
@@ -3711,7 +3778,7 @@
         <v>29</v>
       </c>
       <c r="AX18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AY18" t="n">
         <v>30</v>
@@ -3720,10 +3787,10 @@
         <v>24</v>
       </c>
       <c r="BA18" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BC18" t="n">
         <v>26</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -3755,85 +3822,85 @@
         </is>
       </c>
       <c r="D19" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E19" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F19" t="n">
         <v>18</v>
       </c>
       <c r="G19" t="n">
-        <v>0.486</v>
+        <v>0.471</v>
       </c>
       <c r="H19" t="n">
         <v>48.7</v>
       </c>
       <c r="I19" t="n">
-        <v>35.5</v>
+        <v>35.6</v>
       </c>
       <c r="J19" t="n">
-        <v>81.09999999999999</v>
+        <v>81.40000000000001</v>
       </c>
       <c r="K19" t="n">
-        <v>0.438</v>
+        <v>0.437</v>
       </c>
       <c r="L19" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M19" t="n">
         <v>20.6</v>
       </c>
       <c r="N19" t="n">
-        <v>0.374</v>
+        <v>0.37</v>
       </c>
       <c r="O19" t="n">
         <v>20.6</v>
       </c>
       <c r="P19" t="n">
-        <v>26.4</v>
+        <v>26.1</v>
       </c>
       <c r="Q19" t="n">
-        <v>0.781</v>
+        <v>0.789</v>
       </c>
       <c r="R19" t="n">
-        <v>11.6</v>
+        <v>11.5</v>
       </c>
       <c r="S19" t="n">
-        <v>30</v>
+        <v>29.7</v>
       </c>
       <c r="T19" t="n">
-        <v>41.6</v>
+        <v>41.2</v>
       </c>
       <c r="U19" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="V19" t="n">
-        <v>13.5</v>
+        <v>13.4</v>
       </c>
       <c r="W19" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X19" t="n">
         <v>4.7</v>
       </c>
       <c r="Y19" t="n">
-        <v>5.6</v>
+        <v>5.7</v>
       </c>
       <c r="Z19" t="n">
-        <v>23.4</v>
+        <v>23.5</v>
       </c>
       <c r="AA19" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB19" t="n">
-        <v>99.3</v>
+        <v>99.40000000000001</v>
       </c>
       <c r="AC19" t="n">
-        <v>-2.3</v>
+        <v>-2.6</v>
       </c>
       <c r="AD19" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE19" t="n">
         <v>16</v>
@@ -3851,7 +3918,7 @@
         <v>25</v>
       </c>
       <c r="AJ19" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AK19" t="n">
         <v>26</v>
@@ -3860,25 +3927,25 @@
         <v>6</v>
       </c>
       <c r="AM19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN19" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AO19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AP19" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AQ19" t="n">
         <v>9</v>
       </c>
       <c r="AR19" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AS19" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AT19" t="n">
         <v>17</v>
@@ -3896,19 +3963,19 @@
         <v>19</v>
       </c>
       <c r="AY19" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AZ19" t="n">
         <v>28</v>
       </c>
       <c r="BA19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BB19" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BC19" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="BD19" t="n">
         <v>10</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -4024,7 +4091,7 @@
         <v>5</v>
       </c>
       <c r="AG20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AH20" t="n">
         <v>30</v>
@@ -4036,7 +4103,7 @@
         <v>27</v>
       </c>
       <c r="AK20" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AL20" t="n">
         <v>7</v>
@@ -4066,10 +4133,10 @@
         <v>29</v>
       </c>
       <c r="AU20" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AV20" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AW20" t="n">
         <v>8</v>
@@ -4081,7 +4148,7 @@
         <v>3</v>
       </c>
       <c r="AZ20" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BA20" t="n">
         <v>12</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -4200,13 +4267,13 @@
         <v>24</v>
       </c>
       <c r="AE21" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AG21" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AH21" t="n">
         <v>21</v>
@@ -4230,10 +4297,10 @@
         <v>15</v>
       </c>
       <c r="AO21" t="n">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="AP21" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AQ21" t="n">
         <v>6</v>
@@ -4248,13 +4315,13 @@
         <v>8</v>
       </c>
       <c r="AU21" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV21" t="n">
         <v>22</v>
       </c>
       <c r="AW21" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AX21" t="n">
         <v>30</v>
@@ -4269,7 +4336,7 @@
         <v>28</v>
       </c>
       <c r="BB21" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="BC21" t="n">
         <v>22</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4446,7 @@
         <v>-8.4</v>
       </c>
       <c r="AD22" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE22" t="n">
         <v>30</v>
@@ -4394,7 +4461,7 @@
         <v>27</v>
       </c>
       <c r="AI22" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AJ22" t="n">
         <v>11</v>
@@ -4412,7 +4479,7 @@
         <v>11</v>
       </c>
       <c r="AO22" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AP22" t="n">
         <v>16</v>
@@ -4421,7 +4488,7 @@
         <v>24</v>
       </c>
       <c r="AR22" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AS22" t="n">
         <v>18</v>
@@ -4436,7 +4503,7 @@
         <v>27</v>
       </c>
       <c r="AW22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX22" t="n">
         <v>21</v>
@@ -4445,7 +4512,7 @@
         <v>20</v>
       </c>
       <c r="AZ22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BA22" t="n">
         <v>26</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -4561,10 +4628,10 @@
         <v>7.1</v>
       </c>
       <c r="AD23" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="AE23" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AF23" t="n">
         <v>4</v>
@@ -4579,10 +4646,10 @@
         <v>19</v>
       </c>
       <c r="AJ23" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4594,19 +4661,19 @@
         <v>8</v>
       </c>
       <c r="AO23" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP23" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
       </c>
       <c r="AR23" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AS23" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AT23" t="n">
         <v>9</v>
@@ -4621,7 +4688,7 @@
         <v>11</v>
       </c>
       <c r="AX23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AY23" t="n">
         <v>4</v>
@@ -4633,7 +4700,7 @@
         <v>7</v>
       </c>
       <c r="BB23" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC23" t="n">
         <v>4</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -4746,13 +4813,13 @@
         <v>16</v>
       </c>
       <c r="AE24" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AF24" t="n">
         <v>19</v>
       </c>
       <c r="AG24" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AH24" t="n">
         <v>23</v>
@@ -4761,7 +4828,7 @@
         <v>13</v>
       </c>
       <c r="AJ24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AK24" t="n">
         <v>17</v>
@@ -4776,7 +4843,7 @@
         <v>30</v>
       </c>
       <c r="AO24" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AP24" t="n">
         <v>15</v>
@@ -4791,13 +4858,13 @@
         <v>12</v>
       </c>
       <c r="AT24" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU24" t="n">
         <v>18</v>
       </c>
       <c r="AV24" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AW24" t="n">
         <v>9</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -4925,10 +4992,10 @@
         <v>1.2</v>
       </c>
       <c r="AD25" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AE25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF25" t="n">
         <v>9</v>
@@ -4961,7 +5028,7 @@
         <v>8</v>
       </c>
       <c r="AP25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AQ25" t="n">
         <v>26</v>
@@ -4973,13 +5040,13 @@
         <v>9</v>
       </c>
       <c r="AT25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AU25" t="n">
         <v>11</v>
       </c>
       <c r="AV25" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AW25" t="n">
         <v>27</v>
@@ -4991,13 +5058,13 @@
         <v>7</v>
       </c>
       <c r="AZ25" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BA25" t="n">
         <v>8</v>
       </c>
       <c r="BB25" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BC25" t="n">
         <v>13</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -5029,106 +5096,106 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E26" t="n">
         <v>20</v>
       </c>
       <c r="F26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G26" t="n">
-        <v>0.606</v>
+        <v>0.588</v>
       </c>
       <c r="H26" t="n">
-        <v>48.5</v>
+        <v>48.4</v>
       </c>
       <c r="I26" t="n">
-        <v>36.3</v>
+        <v>36.1</v>
       </c>
       <c r="J26" t="n">
-        <v>79.09999999999999</v>
+        <v>79.2</v>
       </c>
       <c r="K26" t="n">
-        <v>0.459</v>
+        <v>0.455</v>
       </c>
       <c r="L26" t="n">
-        <v>7.8</v>
+        <v>7.9</v>
       </c>
       <c r="M26" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="N26" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="O26" t="n">
-        <v>18.3</v>
+        <v>18</v>
       </c>
       <c r="P26" t="n">
-        <v>23.6</v>
+        <v>23.3</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.775</v>
+        <v>0.771</v>
       </c>
       <c r="R26" t="n">
         <v>13.2</v>
       </c>
       <c r="S26" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="T26" t="n">
-        <v>40.8</v>
+        <v>40.9</v>
       </c>
       <c r="U26" t="n">
         <v>20.6</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
         <v>7</v>
       </c>
       <c r="X26" t="n">
-        <v>5.2</v>
+        <v>5.1</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.5</v>
+        <v>3.6</v>
       </c>
       <c r="Z26" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AA26" t="n">
-        <v>21</v>
+        <v>20.9</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.59999999999999</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.5</v>
+        <v>2.9</v>
       </c>
       <c r="AD26" t="n">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="AE26" t="n">
         <v>10</v>
       </c>
       <c r="AF26" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AG26" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AH26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI26" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AJ26" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AL26" t="n">
         <v>5</v>
@@ -5140,10 +5207,10 @@
         <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="AP26" t="n">
-        <v>19</v>
+        <v>23</v>
       </c>
       <c r="AQ26" t="n">
         <v>11</v>
@@ -5158,31 +5225,31 @@
         <v>19</v>
       </c>
       <c r="AU26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AV26" t="n">
         <v>3</v>
       </c>
       <c r="AW26" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX26" t="n">
         <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ26" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="BA26" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB26" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BC26" t="n">
-        <v>7</v>
+        <v>9</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E27" t="n">
         <v>8</v>
       </c>
       <c r="F27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G27" t="n">
-        <v>0.229</v>
+        <v>0.235</v>
       </c>
       <c r="H27" t="n">
         <v>48.3</v>
@@ -5229,25 +5296,25 @@
         <v>35.9</v>
       </c>
       <c r="J27" t="n">
-        <v>81.09999999999999</v>
+        <v>81</v>
       </c>
       <c r="K27" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L27" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="M27" t="n">
         <v>17.1</v>
       </c>
       <c r="N27" t="n">
-        <v>0.323</v>
+        <v>0.325</v>
       </c>
       <c r="O27" t="n">
-        <v>18.8</v>
+        <v>18.9</v>
       </c>
       <c r="P27" t="n">
-        <v>23.7</v>
+        <v>23.9</v>
       </c>
       <c r="Q27" t="n">
         <v>0.792</v>
@@ -5262,16 +5329,16 @@
         <v>39.5</v>
       </c>
       <c r="U27" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="V27" t="n">
-        <v>15.6</v>
+        <v>15.8</v>
       </c>
       <c r="W27" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="X27" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y27" t="n">
         <v>5.1</v>
@@ -5283,13 +5350,13 @@
         <v>21.4</v>
       </c>
       <c r="AB27" t="n">
-        <v>96.2</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="AC27" t="n">
         <v>-9.199999999999999</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE27" t="n">
         <v>26</v>
@@ -5301,7 +5368,7 @@
         <v>28</v>
       </c>
       <c r="AH27" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI27" t="n">
         <v>21</v>
@@ -5310,7 +5377,7 @@
         <v>14</v>
       </c>
       <c r="AK27" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AL27" t="n">
         <v>20</v>
@@ -5340,25 +5407,25 @@
         <v>26</v>
       </c>
       <c r="AU27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV27" t="n">
+        <v>25</v>
+      </c>
+      <c r="AW27" t="n">
         <v>24</v>
-      </c>
-      <c r="AW27" t="n">
-        <v>23</v>
       </c>
       <c r="AX27" t="n">
         <v>24</v>
       </c>
       <c r="AY27" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AZ27" t="n">
         <v>29</v>
       </c>
       <c r="BA27" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="BB27" t="n">
         <v>21</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -5393,16 +5460,16 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F28" t="n">
         <v>11</v>
       </c>
       <c r="G28" t="n">
-        <v>0.676</v>
+        <v>0.667</v>
       </c>
       <c r="H28" t="n">
         <v>48.9</v>
@@ -5411,7 +5478,7 @@
         <v>36.8</v>
       </c>
       <c r="J28" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="K28" t="n">
         <v>0.466</v>
@@ -5423,28 +5490,28 @@
         <v>20.7</v>
       </c>
       <c r="N28" t="n">
-        <v>0.407</v>
+        <v>0.406</v>
       </c>
       <c r="O28" t="n">
-        <v>14.9</v>
+        <v>15</v>
       </c>
       <c r="P28" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.75</v>
+        <v>0.751</v>
       </c>
       <c r="R28" t="n">
-        <v>8.300000000000001</v>
+        <v>8.4</v>
       </c>
       <c r="S28" t="n">
-        <v>31.7</v>
+        <v>31.6</v>
       </c>
       <c r="T28" t="n">
         <v>40</v>
       </c>
       <c r="U28" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="V28" t="n">
         <v>12.2</v>
@@ -5453,25 +5520,25 @@
         <v>5.4</v>
       </c>
       <c r="X28" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.2</v>
+        <v>4.3</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.7</v>
+        <v>18.9</v>
       </c>
       <c r="AB28" t="n">
-        <v>96.90000000000001</v>
+        <v>97.09999999999999</v>
       </c>
       <c r="AC28" t="n">
-        <v>3.4</v>
+        <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="AE28" t="n">
         <v>6</v>
@@ -5483,10 +5550,10 @@
         <v>5</v>
       </c>
       <c r="AH28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AJ28" t="n">
         <v>20</v>
@@ -5498,7 +5565,7 @@
         <v>3</v>
       </c>
       <c r="AM28" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AN28" t="n">
         <v>1</v>
@@ -5531,22 +5598,22 @@
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AY28" t="n">
         <v>8</v>
       </c>
       <c r="AZ28" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA28" t="n">
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -5575,61 +5642,61 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E29" t="n">
         <v>14</v>
       </c>
       <c r="F29" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="G29" t="n">
-        <v>0.4</v>
+        <v>0.412</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>35.9</v>
+        <v>35.8</v>
       </c>
       <c r="J29" t="n">
-        <v>79</v>
+        <v>79.2</v>
       </c>
       <c r="K29" t="n">
-        <v>0.454</v>
+        <v>0.452</v>
       </c>
       <c r="L29" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="M29" t="n">
-        <v>16.8</v>
+        <v>16.9</v>
       </c>
       <c r="N29" t="n">
-        <v>0.378</v>
+        <v>0.377</v>
       </c>
       <c r="O29" t="n">
-        <v>18.9</v>
+        <v>19.1</v>
       </c>
       <c r="P29" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.826</v>
+        <v>0.83</v>
       </c>
       <c r="R29" t="n">
-        <v>9</v>
+        <v>9.1</v>
       </c>
       <c r="S29" t="n">
-        <v>30.1</v>
+        <v>30.2</v>
       </c>
       <c r="T29" t="n">
-        <v>39.1</v>
+        <v>39.3</v>
       </c>
       <c r="U29" t="n">
-        <v>22.1</v>
+        <v>21.9</v>
       </c>
       <c r="V29" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="W29" t="n">
         <v>6.5</v>
@@ -5638,55 +5705,55 @@
         <v>5.1</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="AA29" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AB29" t="n">
         <v>97</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.9</v>
+        <v>-2.7</v>
       </c>
       <c r="AD29" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE29" t="n">
         <v>18</v>
       </c>
       <c r="AF29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AG29" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AH29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AI29" t="n">
         <v>24</v>
       </c>
       <c r="AJ29" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AK29" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AL29" t="n">
         <v>17</v>
       </c>
       <c r="AM29" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AN29" t="n">
         <v>9</v>
       </c>
       <c r="AO29" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AP29" t="n">
         <v>24</v>
@@ -5698,22 +5765,22 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AT29" t="n">
         <v>27</v>
       </c>
       <c r="AU29" t="n">
+        <v>8</v>
+      </c>
+      <c r="AV29" t="n">
         <v>6</v>
-      </c>
-      <c r="AV29" t="n">
-        <v>7</v>
       </c>
       <c r="AW29" t="n">
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AY29" t="n">
         <v>13</v>
@@ -5725,7 +5792,7 @@
         <v>19</v>
       </c>
       <c r="BB29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BC29" t="n">
         <v>21</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -5757,25 +5824,25 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="E30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="F30" t="n">
         <v>15</v>
       </c>
       <c r="G30" t="n">
-        <v>0.571</v>
+        <v>0.5590000000000001</v>
       </c>
       <c r="H30" t="n">
         <v>48.6</v>
       </c>
       <c r="I30" t="n">
-        <v>37.9</v>
+        <v>37.8</v>
       </c>
       <c r="J30" t="n">
-        <v>80.09999999999999</v>
+        <v>79.90000000000001</v>
       </c>
       <c r="K30" t="n">
         <v>0.473</v>
@@ -5787,67 +5854,67 @@
         <v>13</v>
       </c>
       <c r="N30" t="n">
-        <v>0.33</v>
+        <v>0.333</v>
       </c>
       <c r="O30" t="n">
-        <v>20.9</v>
+        <v>20.6</v>
       </c>
       <c r="P30" t="n">
-        <v>27.1</v>
+        <v>26.7</v>
       </c>
       <c r="Q30" t="n">
         <v>0.77</v>
       </c>
       <c r="R30" t="n">
-        <v>12.4</v>
+        <v>12.2</v>
       </c>
       <c r="S30" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T30" t="n">
-        <v>42.1</v>
+        <v>41.9</v>
       </c>
       <c r="U30" t="n">
         <v>24.8</v>
       </c>
       <c r="V30" t="n">
-        <v>16</v>
+        <v>16.1</v>
       </c>
       <c r="W30" t="n">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="X30" t="n">
         <v>5.1</v>
       </c>
       <c r="Y30" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Z30" t="n">
         <v>22.5</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.4</v>
+        <v>23.3</v>
       </c>
       <c r="AB30" t="n">
-        <v>101</v>
+        <v>100.5</v>
       </c>
       <c r="AC30" t="n">
         <v>2.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AE30" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="AF30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AG30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AH30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI30" t="n">
         <v>5</v>
@@ -5856,7 +5923,7 @@
         <v>16</v>
       </c>
       <c r="AK30" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AL30" t="n">
         <v>28</v>
@@ -5865,40 +5932,40 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AO30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP30" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AQ30" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AR30" t="n">
         <v>6</v>
       </c>
       <c r="AS30" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AT30" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AU30" t="n">
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AY30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AZ30" t="n">
         <v>25</v>
@@ -5907,10 +5974,10 @@
         <v>3</v>
       </c>
       <c r="BB30" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC30" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
@@ -6044,13 +6111,13 @@
         <v>22</v>
       </c>
       <c r="AM31" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AN31" t="n">
         <v>29</v>
       </c>
       <c r="AO31" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AP31" t="n">
         <v>25</v>
@@ -6065,10 +6132,10 @@
         <v>27</v>
       </c>
       <c r="AT31" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AU31" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-5-2008-09</t>
+          <t>2009-01-05</t>
         </is>
       </c>
     </row>
